--- a/Compititor's_Price/Celotex_Prices/Celotex_Prices_08-02-2026.xlsx
+++ b/Compititor's_Price/Celotex_Prices/Celotex_Prices_08-02-2026.xlsx
@@ -665,7 +665,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>£13.07</t>
+          <t>Error: HTTPSConnectionPool(host='www.insulation-online.com', port=443): Read timed out.</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -700,7 +700,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>£13.05</t>
+          <t>Price Not Found</t>
         </is>
       </c>
     </row>
@@ -1657,7 +1657,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>£39.08</t>
+          <t>Error: HTTPSConnectionPool(host='www.insulationuk.co.uk', port=443): Max retries exceeded with url: /products/130mm-celotex-xr4130-pir-insulation-board-2400mm-x-1200mm-x-130mm (Caused by SSLError(SSLEOFError(8, '[SSL: UNEXPECTED_EOF_WHILE_READING] EOF occurred in violation of protocol (_ssl.c:1006)')))</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1682,7 +1682,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t>Error: HTTPSConnectionPool(host='www.planetinsulation.co.uk', port=443): Read timed out.</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>£57.54</t>
+          <t>Error: HTTPSConnectionPool(host='www.insulation-online.com', port=443): Max retries exceeded with url: /product/celotex-pl4050-63mm/ (Caused by SSLError(SSLEOFError(8, '[SSL: UNEXPECTED_EOF_WHILE_READING] EOF occurred in violation of protocol (_ssl.c:1006)')))</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -2413,7 +2413,7 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>£61.03</t>
+          <t>Error: HTTPSConnectionPool(host='www.insulation-online.com', port=443): Read timed out. (read timeout=30)</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -3057,7 +3057,7 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>£1206.21</t>
+          <t>Error: ('Connection aborted.', ConnectionResetError(10054, 'An existing connection was forcibly closed by the remote host', None, 10054, None))</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
